--- a/vault-dalarna-university/04 ISLL/Analys/Programkurser olankade.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Programkurser olankade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olankade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olankade'!$A$1:$E$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olankade'!$A$1:$E$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1390,7 +1390,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HMILA</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`Valbara eller valfria litteraturvetenskapligt inriktade kurser` (30 hp); rad: - Valbara eller valfria litteraturvetenskapligt inriktade kurser, 30 hp</t>
+          <t>Programtext `Afrikanska samhällen i förändring` ≠ kursplanens namn `Afrikanska studier: Afrikanska samhällen i förändring` (kurskod `AS3022`); rad: - [[AS3022|Afrikanska samhällen i förändring]], 12 hp</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HMILA</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Valbara och valfria litteraturvetenskapligt inriktade kurser` (30 hp); rad: - Valbara och valfria litteraturvetenskapligt inriktade kurser, 30 hp</t>
+          <t>Programtext `Religion och politik i afrikanska samhällen` ≠ kursplanens namn `Afrikanska studier: Religion och politik i afrikanska samhällen` (kurskod `AS3023`); rad: - [[AS3023|Religion och politik i afrikanska samhällen]], 9 hp</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HMILA</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Valbar eller valfri kurs inom franskspråkig litteratur` (7,5 hp); rad: - Valbar eller valfri kurs inom franskspråkig litteratur, 7,5 hp</t>
+          <t>Programtext `Utbildning och förändring i afrikanska samhällen` ≠ kursplanens namn `Afrikanska studier: Utbildning och förändring i afrikanska samhällen` (kurskod `AS3021`); rad: - [[AS3021|Utbildning och förändring i afrikanska samhällen]], 8 hp</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HMILA</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Valbar eller valfri kurs inom tyskspråkig litteratur` (7,5 hp); rad: - Valbar eller valfri kurs inom tyskspråkig litteratur, 7,5 hp</t>
+          <t>Programtext `Litteratur och politik i det samtida Afrika` ≠ kursplanens namn `Afrikanska studier: Litteratur och politik i det samtida Afrika` (kurskod `AS3017`); rad: - [[AS3017|Litteratur och politik i det samtida Afrika]], 7 hp</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HSVAA</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv` (7,5 hp); rad: - Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv, 7,5 hp</t>
+          <t>Programtext `Ekonomisk utveckling i Afrika, en introduktion` ≠ kursplanens namn `Afrikanska studier: Ekonomisk utveckling i Afrika, en introduktion` (kurskod `AS3019`); rad: - [[AS3019|Ekonomisk utveckling i Afrika, en introduktion]], 7 hp</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HSVAA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HTESA</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`Kärnområden i tillämpad engelsk lingvistik` (7,5 hp); rad: - Kärnområden i tillämpad engelsk lingvistik, 7,5 hp</t>
+          <t>Programtext `Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv` ≠ kursplanens namn `Afrikanska studier: Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv` (kurskod `AS3014`); rad: - [[AS3014|Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv]], 7hp</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HTESA</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
+          <t>Programtext `Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara` ≠ kursplanens namn `Afrikanska studier: Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara` (kurskod `AS3018`); rad: - [[AS3018|Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara]], 7 hp</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>HMILA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Bullet beskriver val mellan flera kurser</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Valbara eller valfria litteraturvetenskapligt inriktade kurser` (30 hp); rad: - Valbara eller valfria litteraturvetenskapligt inriktade kurser, 30 hp</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>HMILA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Bullet beskriver val mellan flera kurser</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>`Valbara och valfria litteraturvetenskapligt inriktade kurser` (30 hp); rad: - Valbara och valfria litteraturvetenskapligt inriktade kurser, 30 hp</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>HMILA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Bullet beskriver val mellan flera kurser</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Valbar eller valfri kurs inom franskspråkig litteratur` (7,5 hp); rad: - Valbar eller valfri kurs inom franskspråkig litteratur, 7,5 hp</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>HMILA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Bullet beskriver val mellan flera kurser</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Valbar eller valfri kurs inom tyskspråkig litteratur` (7,5 hp); rad: - Valbar eller valfri kurs inom tyskspråkig litteratur, 7,5 hp</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>HMILA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>Programtext `Franskspråkig chanson i original och översättning` ≠ kursplanens namn `Franska IV: Franskspråkig chanson i original och översättning` (kurskod `AFR27P`); rad: - [[AFR27P|Franskspråkig chanson i original och översättning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>HMILA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>Programtext `Franskspråkig litteraturkritik` ≠ kursplanens namn `Franska IV: Franskspråkig litteraturkritik` (kurskod `AFR26Q`); rad: - [[AFR26Q|Franskspråkig litteraturkritik]], 7,5 hp</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>HSVAA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv` (7,5 hp); rad: - Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HSVAA</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>HTESA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Kärnområden i tillämpad engelsk lingvistik` (7,5 hp); rad: - Kärnområden i tillämpad engelsk lingvistik, 7,5 hp</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>HTESA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>HTESA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`Examensarbete i ämne 1 eller 2` (30 hp); rad: - Examensarbete i ämne 1 eller 2, 30 hp</t>
+          <t>Programtext `Diskursanalys` ≠ kursplanens namn `Engelska: Diskursanalys` (kurskod `EN3072`); rad: - [[EN3072|Diskursanalys]], 7,5 hp</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1923,14 +1923,14 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1950,14 +1950,14 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2004,14 +2004,14 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2031,14 +2031,14 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Bullet beskriver val mellan flera kurser</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Examensarbete i ämne 1 eller 2` (30 hp); rad: - Examensarbete i ämne 1 eller 2, 30 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - &lt;a class="no-graph" href="GPG32A"&gt;Skolväsendets historia och samhällsuppdrag – ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`Examensarbete i ämne 1 eller 2` (30 hp); rad: - Examensarbete i ämne 1 eller 2, 30 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1A` (15 hp); rad: - Engelska för grundlärare åk 4-6 1A, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1B` (15 hp); rad: - Engelska för grundlärare åk 4-6 1B, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Bullet beskriver val mellan flera kurser</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Examensarbete i ämne 1 eller 2` (30 hp); rad: - Examensarbete i ämne 1 eller 2, 30 hp</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2480,24 +2480,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - &lt;a class="no-graph" href="GPG32A"&gt;Skolväsendets historia och samhällsuppdrag – ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1A` (15 hp); rad: - Engelska för grundlärare åk 4-6 1A, 15 hp</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1B` (15 hp); rad: - Engelska för grundlärare åk 4-6 1B, 15 hp</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
+          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2723,24 +2723,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2777,24 +2777,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i grundskolan åk 4–6` ≠ kursplanens namn `Sociala relationer, konflikter och makt i grundskolan åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG2LZ`); rad: - &lt;a class="no-graph" href="GPG2LZ"&gt;Sociala relationer, konflikter och makt i grundskolan åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2804,24 +2804,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>Programtext `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6` ≠ kursplanens namn `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4-6` (kurskod `PG3025`); rad: - &lt;a class="no-graph" href="PG3025"&gt;Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4-6` (kurskod `APG245`); rad: - &lt;a class="no-graph" href="APG245"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2858,24 +2858,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>Programtext `Matematik 1a för grundlärare 4–6` ≠ kursplanens namn `Matematik 1a för grundlärare 4-6` (kurskod `GMD2HH`); rad: - &lt;a class="no-graph" href="GMD2HH"&gt;Matematik 1a för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>Programtext `Matematik 1b för grundlärare 4–6` ≠ kursplanens namn `Matematik 1b för grundlärare 4-6` (kurskod `GMD2HJ`); rad: - &lt;a class="no-graph" href="GMD2HJ"&gt;Matematik 1b för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2912,24 +2912,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>Programtext `Matematik 2 för grundlärare 4–6` ≠ kursplanens namn `Matematik 2 för grundlärare 4-6` (kurskod `GMD2HK`); rad: - &lt;a class="no-graph" href="GMD2HK"&gt;Matematik 2 för grundlärare 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2939,24 +2939,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2966,24 +2966,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2993,24 +2993,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
+          <t>Programtext `Bild för grundlärare, årskurs 4–6` ≠ kursplanens namn `Bild för grundlärare, årskurs 4-6` (kurskod `GBP32U`); rad: - &lt;a class="no-graph" href="GBP32U"&gt;Bild för grundlärare, årskurs 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3020,24 +3020,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>LYSLA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3047,24 +3047,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
+          <t>Programtext `Naturorienterande ämnen och teknik för grundlärare, åk 4–6` ≠ kursplanens namn `Naturorienterande ämnen och teknik för grundlärare, åk 4-6` (kurskod `GNV367`); rad: - &lt;a class="no-graph" href="GNV367"&gt;Naturorienterande ämnen och teknik för grundlärare, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>LYSLA</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3079,44 +3079,2015 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>LLF3A</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>LLF3A</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>LLF3A</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>LLF3A</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>LLF3A</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>LLF3A</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>LLF3A</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>LLF3A</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>LLF3A</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>LLL3A</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>LLL3A</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>LLL3A</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>LLL3A</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>LLL3A</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>LLL3A</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>LLL3A</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>LLL3A</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>LLL3A</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>LLL3A</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Programtext `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6` ≠ kursplanens namn `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4-6` (kurskod `PG3025`); rad: - &lt;a class="no-graph" href="PG3025"&gt;Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4-6` (kurskod `APG245`); rad: - &lt;a class="no-graph" href="APG245"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Programtext `Matematik 1a för grundlärare 4–6` ≠ kursplanens namn `Matematik 1a för grundlärare 4-6` (kurskod `GMD2HH`); rad: - &lt;a class="no-graph" href="GMD2HH"&gt;Matematik 1a för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Programtext `Matematik 1b för grundlärare 4–6` ≠ kursplanens namn `Matematik 1b för grundlärare 4-6` (kurskod `GMD2HJ`); rad: - &lt;a class="no-graph" href="GMD2HJ"&gt;Matematik 1b för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Programtext `Matematik 2 för grundlärare 4–6` ≠ kursplanens namn `Matematik 2 för grundlärare 4-6` (kurskod `GMD2HK`); rad: - &lt;a class="no-graph" href="GMD2HK"&gt;Matematik 2 för grundlärare 4–6&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Programtext `Bild för grundlärare, årskurs 4–6` ≠ kursplanens namn `Bild för grundlärare, årskurs 4-6` (kurskod `GBP32U`); rad: - &lt;a class="no-graph" href="GBP32U"&gt;Bild för grundlärare, årskurs 4–6&lt;/a&gt;, 30 hp</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>LLL6A</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Programtext `Naturorienterande ämnen och teknik för grundlärare, åk 4–6` ≠ kursplanens namn `Naturorienterande ämnen och teknik för grundlärare, åk 4-6` (kurskod `GNV367`); rad: - &lt;a class="no-graph" href="GNV367"&gt;Naturorienterande ämnen och teknik för grundlärare, åk 4–6&lt;/a&gt;, 30 hp</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Programtext `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6` ≠ kursplanens namn `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4-6` (kurskod `PG3025`); rad: - &lt;a class="no-graph" href="PG3025"&gt;Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4-6` (kurskod `APG245`); rad: - &lt;a class="no-graph" href="APG245"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Programtext `Matematik 1a för grundlärare 4–6` ≠ kursplanens namn `Matematik 1a för grundlärare 4-6` (kurskod `GMD2HH`); rad: - &lt;a class="no-graph" href="GMD2HH"&gt;Matematik 1a för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Programtext `Matematik 1b för grundlärare 4–6` ≠ kursplanens namn `Matematik 1b för grundlärare 4-6` (kurskod `GMD2HJ`); rad: - &lt;a class="no-graph" href="GMD2HJ"&gt;Matematik 1b för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Programtext `Matematik 2 för grundlärare 4–6` ≠ kursplanens namn `Matematik 2 för grundlärare 4-6` (kurskod `GMD2HK`); rad: - &lt;a class="no-graph" href="GMD2HK"&gt;Matematik 2 för grundlärare 4–6&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Programtext `Bild för grundlärare, årskurs 4–6` ≠ kursplanens namn `Bild för grundlärare, årskurs 4-6` (kurskod `GBP32U`); rad: - &lt;a class="no-graph" href="GBP32U"&gt;Bild för grundlärare, årskurs 4–6&lt;/a&gt;, 30 hp</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>LLP6A</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Programtext `Naturorienterande ämnen och teknik för grundlärare, åk 4–6` ≠ kursplanens namn `Naturorienterande ämnen och teknik för grundlärare, åk 4-6` (kurskod `GNV367`); rad: - &lt;a class="no-graph" href="GNV367"&gt;Naturorienterande ämnen och teknik för grundlärare, åk 4–6&lt;/a&gt;, 30 hp</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>LU79A</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>LU79A</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Programtext `Kunskap, lärande och bedömning – KPU` ≠ kursplanens namn `Kunskap, lärande och bedömning - KPU` (kurskod `GPG2S7`); rad: - &lt;a class="no-graph" href="GPG2S7"&gt;Kunskap, lärande och bedömning – KPU&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>LU79A</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>LU79A</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>LU79A</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>LUGYA</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>LUGYA</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Programtext `Kunskap, lärande och bedömning – KPU` ≠ kursplanens namn `Kunskap, lärande och bedömning - KPU` (kurskod `GPG2S7`); rad: - &lt;a class="no-graph" href="GPG2S7"&gt;Kunskap, lärande och bedömning – KPU&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>LUGYA</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>LUGYA</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>LUGYA</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
           <t>LYSLA</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>LYSLA</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>LYSLA</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
         <is>
           <t>`Professionellt lärarskap och skolutveckling` (15 hp); rad: - Professionellt lärarskap och skolutveckling, 15 hp</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E99"/>
+  <autoFilter ref="A1:E172"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3314,6 +5285,152 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
